--- a/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Batteries</t>
         </is>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>6.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Bois De Chauffe</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Piles</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -490,12 +472,6 @@
           <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -611,12 +587,6 @@
           <t>Batteries</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -647,12 +617,6 @@
           <t>Piles</t>
         </is>
       </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -696,12 +660,6 @@
           <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -714,12 +672,6 @@
           <t>Batteries</t>
         </is>
       </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -732,12 +684,6 @@
           <t>Bois De Chauffe</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -750,12 +696,6 @@
           <t>Electricité Réseau</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -768,12 +708,6 @@
           <t>Groupe Électrogène</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -804,12 +738,6 @@
           <t>Piles</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -853,12 +781,6 @@
           <t>Alaotra - Analamiranga</t>
         </is>
       </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -907,12 +829,6 @@
           <t>Piles</t>
         </is>
       </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1059,12 +975,6 @@
           <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-      <c r="D41">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1095,12 +1005,6 @@
           <t>Groupe Électrogène</t>
         </is>
       </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1180,12 +1084,6 @@
           <t>Alaotra - Mangabe</t>
         </is>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1319,12 +1217,6 @@
           <t>Bois De Chauffe</t>
         </is>
       </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1337,12 +1229,6 @@
           <t>Electricité Réseau</t>
         </is>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1354,12 +1240,6 @@
         <is>
           <t>Groupe Électrogène</t>
         </is>
-      </c>
-      <c r="C58">
-        <v>3</v>
-      </c>
-      <c r="D58">
-        <v>0.3</v>
       </c>
     </row>
     <row r="59">

--- a/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,14 +408,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>20.4</v>
+          <t>Piles</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -426,8 +420,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piles</t>
-        </is>
+          <t>Pétrole Lampant</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>74.2</v>
       </c>
     </row>
     <row r="6">
@@ -438,32 +438,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>46.9</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>22.4</v>
+          <t>Alaotra - Ambatomanga</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -472,6 +461,17 @@
           <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Batteries</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -481,14 +481,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>5.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="10">
@@ -499,14 +499,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10">
-        <v>25.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="11">
@@ -517,50 +517,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>9.300000000000001</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="C12">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>29.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>33</v>
-      </c>
-      <c r="D13">
-        <v>28</v>
+          <t>Batteries</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -569,11 +558,10 @@
           <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>4.8</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Piles</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -584,8 +572,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Batteries</t>
-        </is>
+          <t>Pétrole Lampant</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>44.8</v>
       </c>
     </row>
     <row r="16">
@@ -596,62 +590,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C16">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D16">
-        <v>29.5</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Piles</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>26</v>
-      </c>
-      <c r="D18">
-        <v>24.8</v>
+          <t>Batteries</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>36</v>
-      </c>
-      <c r="D19">
-        <v>34.3</v>
+          <t>Bois De Chauffe</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -660,6 +637,11 @@
           <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Electricité Réseau</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -669,7 +651,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>Groupe Électrogène</t>
         </is>
       </c>
     </row>
@@ -681,7 +663,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
+          <t>Piles</t>
         </is>
       </c>
     </row>
@@ -693,8 +675,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Electricité Réseau</t>
-        </is>
+          <t>Pétrole Lampant</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -705,74 +693,69 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Groupe Électrogène</t>
-        </is>
+          <t>Solaire</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>42.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>17</v>
-      </c>
-      <c r="D25">
-        <v>20.2</v>
+          <t>Alaotra - Analamiranga</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Piles</t>
-        </is>
+          <t>Batteries</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>10.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>34</v>
-      </c>
-      <c r="D27">
-        <v>40.5</v>
+          <t>Piles</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Solaire</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D28">
-        <v>26.2</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="29">
@@ -781,59 +764,71 @@
           <t>Alaotra - Analamiranga</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Solaire</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>21</v>
+      </c>
+      <c r="D29">
+        <v>45.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Batteries</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D31">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Piles</t>
         </is>
+      </c>
+      <c r="C32">
+        <v>22</v>
+      </c>
+      <c r="D32">
+        <v>24.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -842,16 +837,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D33">
-        <v>33.3</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -860,29 +855,23 @@
         </is>
       </c>
       <c r="C34">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D34">
-        <v>26.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>6</v>
-      </c>
-      <c r="D35">
-        <v>3.4</v>
+          <t>Alaotra - Feramanga Atsimo</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -894,31 +883,25 @@
         <v>14</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>42</v>
-      </c>
-      <c r="D37">
-        <v>24.1</v>
+          <t>Groupe Électrogène</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -927,16 +910,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>12.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -945,16 +928,16 @@
         </is>
       </c>
       <c r="C39">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D39">
-        <v>30.5</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -963,23 +946,23 @@
         </is>
       </c>
       <c r="C40">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D40">
-        <v>21.3</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -988,143 +971,137 @@
         </is>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>8.6</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Groupe Électrogène</t>
-        </is>
+          <t>Piles</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>10</v>
+      </c>
+      <c r="D43">
+        <v>13.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C44">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D44">
-        <v>25.2</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D45">
-        <v>6.1</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="C46">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D46">
-        <v>33.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Solaire</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C47">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D47">
-        <v>23.9</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bois De Chauffe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>9</v>
-      </c>
-      <c r="D49">
-        <v>6.3</v>
+          <t>Electricité Réseau</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>41</v>
-      </c>
-      <c r="D50">
-        <v>28.9</v>
+          <t>Groupe Électrogène</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1133,16 +1110,16 @@
         </is>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1151,16 +1128,16 @@
         </is>
       </c>
       <c r="C52">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="D52">
-        <v>26.8</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1169,149 +1146,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="D53">
-        <v>29.6</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>22</v>
-      </c>
-      <c r="D54">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="C55">
-        <v>59</v>
-      </c>
-      <c r="D55">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Bois De Chauffe</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Electricité Réseau</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Groupe Électrogène</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Panneau Solaire En Marche ?</t>
-        </is>
-      </c>
-      <c r="C59">
-        <v>232</v>
-      </c>
-      <c r="D59">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Piles</t>
-        </is>
-      </c>
-      <c r="C60">
-        <v>63</v>
-      </c>
-      <c r="D60">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C61">
-        <v>290</v>
-      </c>
-      <c r="D61">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C62">
-        <v>241</v>
-      </c>
-      <c r="D62">
-        <v>26.4</v>
+        <v>47.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_lighting_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -403,7 +403,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -451,14 +451,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="C12">
@@ -543,7 +543,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -603,14 +603,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -706,14 +706,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="C30">
@@ -792,7 +792,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -864,14 +864,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -955,14 +955,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1034,7 +1034,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C46">
@@ -1047,7 +1047,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
